--- a/output_data/charts/M100000US3902680.xlsx
+++ b/output_data/charts/M100000US3902680.xlsx
@@ -170,10 +170,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -248,16 +248,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -331,6 +334,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -361,10 +367,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -439,16 +445,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$26</c:f>
+              <c:f>Sheet1!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -522,6 +531,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -552,10 +564,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -630,16 +642,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$26</c:f>
+              <c:f>Sheet1!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -714,6 +729,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -743,10 +761,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -821,16 +839,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$26</c:f>
+              <c:f>Sheet1!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -904,6 +925,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -934,10 +958,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1012,16 +1036,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$26</c:f>
+              <c:f>Sheet1!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1095,6 +1122,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1125,10 +1155,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1203,16 +1233,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$26</c:f>
+              <c:f>Sheet1!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1286,6 +1319,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1316,10 +1352,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1394,16 +1430,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$26</c:f>
+              <c:f>Sheet1!$H$2:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1477,6 +1516,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1886,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
@@ -2575,6 +2617,32 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
